--- a/core/ecos/dev-template.xlsx
+++ b/core/ecos/dev-template.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WBG\Anaconda3\Lib\sprnldata\core\ecos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\anaconda3\Lib\sprnldata\core\ecos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5D17749-1DE4-4956-BCA5-C6F77FB7FA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{881B894D-1018-4A79-93C7-7BAB6FC2177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{36412438-C21D-4853-9A0B-9D97E570583D}"/>
+    <workbookView xWindow="-28910" yWindow="10" windowWidth="29020" windowHeight="15820" xr2:uid="{36412438-C21D-4853-9A0B-9D97E570583D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
+    <sheet name="dropdown" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,33 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t>database</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>database1</t>
-  </si>
-  <si>
-    <t>weo_weo_live</t>
-  </si>
-  <si>
-    <t>indicator</t>
-  </si>
-  <si>
-    <t>partner ifs_code</t>
-  </si>
-  <si>
-    <t>freq</t>
-  </si>
-  <si>
-    <t>countries</t>
-  </si>
-  <si>
-    <t>ifs_code (myself)</t>
   </si>
   <si>
     <t>Section 1</t>
@@ -73,17 +48,86 @@
     <t>Section 2</t>
   </si>
   <si>
-    <t>Multiple Version</t>
+    <t>Database</t>
   </si>
   <si>
-    <t>all</t>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Start Year</t>
+  </si>
+  <si>
+    <t>End Year</t>
+  </si>
+  <si>
+    <t>Country List</t>
+  </si>
+  <si>
+    <t>WEO_WEO_PUBLISHED</t>
+  </si>
+  <si>
+    <t>countrylist</t>
+  </si>
+  <si>
+    <t>Enter myself</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>ifscode</t>
+  </si>
+  <si>
+    <t>Counterparty ifscode</t>
+  </si>
+  <si>
+    <t>All countries w/o aggregates</t>
+  </si>
+  <si>
+    <t>All countries w aggregates (WLD, WAEMU, EURO, and ECCU)</t>
+  </si>
+  <si>
+    <t>WEO_WEO_LIVE</t>
+  </si>
+  <si>
+    <t>ECDATA_BOP</t>
+  </si>
+  <si>
+    <t>ECDATA_IFS</t>
+  </si>
+  <si>
+    <t>WEO_GEE_LIVE</t>
+  </si>
+  <si>
+    <t>Section 3</t>
+  </si>
+  <si>
+    <t>Section 4</t>
+  </si>
+  <si>
+    <t>Section 5</t>
+  </si>
+  <si>
+    <t>frequency</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>NGDP</t>
+  </si>
+  <si>
+    <t>BCA_BP6_USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,16 +135,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -108,12 +184,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,93 +519,2774 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B302597-8FD2-424D-9BB1-91CB2179E335}">
-  <dimension ref="A5:I11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:S150"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="Q2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="Q3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="I4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="M4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="Q4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1990</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="I5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="M5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="Q5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2000</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2020</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="I6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="M6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="Q6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I5" t="s">
+      <c r="C7" s="3"/>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="G7" s="3"/>
+      <c r="I7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="M7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="Q7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>11</v>
-      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>111</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>111</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="3"/>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3"/>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+      <c r="S103" s="3"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+      <c r="S104" s="3"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="Q105" s="3"/>
+      <c r="R105" s="3"/>
+      <c r="S105" s="3"/>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3"/>
+      <c r="S106" s="3"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+      <c r="Q107" s="3"/>
+      <c r="R107" s="3"/>
+      <c r="S107" s="3"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3"/>
+      <c r="S108" s="3"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3"/>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+      <c r="O110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3"/>
+      <c r="S110" s="3"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="3"/>
+      <c r="Q111" s="3"/>
+      <c r="R111" s="3"/>
+      <c r="S111" s="3"/>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="O112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3"/>
+      <c r="S112" s="3"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="3"/>
+      <c r="Q113" s="3"/>
+      <c r="R113" s="3"/>
+      <c r="S113" s="3"/>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3"/>
+      <c r="S114" s="3"/>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+      <c r="O115" s="3"/>
+      <c r="Q115" s="3"/>
+      <c r="R115" s="3"/>
+      <c r="S115" s="3"/>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+      <c r="O116" s="3"/>
+      <c r="Q116" s="3"/>
+      <c r="R116" s="3"/>
+      <c r="S116" s="3"/>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+      <c r="O117" s="3"/>
+      <c r="Q117" s="3"/>
+      <c r="R117" s="3"/>
+      <c r="S117" s="3"/>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+      <c r="O118" s="3"/>
+      <c r="Q118" s="3"/>
+      <c r="R118" s="3"/>
+      <c r="S118" s="3"/>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+      <c r="Q119" s="3"/>
+      <c r="R119" s="3"/>
+      <c r="S119" s="3"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+      <c r="O120" s="3"/>
+      <c r="Q120" s="3"/>
+      <c r="R120" s="3"/>
+      <c r="S120" s="3"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+      <c r="O121" s="3"/>
+      <c r="Q121" s="3"/>
+      <c r="R121" s="3"/>
+      <c r="S121" s="3"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+      <c r="Q122" s="3"/>
+      <c r="R122" s="3"/>
+      <c r="S122" s="3"/>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3"/>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3"/>
+      <c r="O123" s="3"/>
+      <c r="Q123" s="3"/>
+      <c r="R123" s="3"/>
+      <c r="S123" s="3"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+      <c r="O124" s="3"/>
+      <c r="Q124" s="3"/>
+      <c r="R124" s="3"/>
+      <c r="S124" s="3"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="Q125" s="3"/>
+      <c r="R125" s="3"/>
+      <c r="S125" s="3"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="Q126" s="3"/>
+      <c r="R126" s="3"/>
+      <c r="S126" s="3"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3"/>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
+      <c r="Q127" s="3"/>
+      <c r="R127" s="3"/>
+      <c r="S127" s="3"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="3"/>
+      <c r="Q128" s="3"/>
+      <c r="R128" s="3"/>
+      <c r="S128" s="3"/>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3"/>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3"/>
+      <c r="O129" s="3"/>
+      <c r="Q129" s="3"/>
+      <c r="R129" s="3"/>
+      <c r="S129" s="3"/>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="3"/>
+      <c r="Q130" s="3"/>
+      <c r="R130" s="3"/>
+      <c r="S130" s="3"/>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+      <c r="O131" s="3"/>
+      <c r="Q131" s="3"/>
+      <c r="R131" s="3"/>
+      <c r="S131" s="3"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+      <c r="O132" s="3"/>
+      <c r="Q132" s="3"/>
+      <c r="R132" s="3"/>
+      <c r="S132" s="3"/>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
+      <c r="Q133" s="3"/>
+      <c r="R133" s="3"/>
+      <c r="S133" s="3"/>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+      <c r="O134" s="3"/>
+      <c r="Q134" s="3"/>
+      <c r="R134" s="3"/>
+      <c r="S134" s="3"/>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3"/>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3"/>
+      <c r="O135" s="3"/>
+      <c r="Q135" s="3"/>
+      <c r="R135" s="3"/>
+      <c r="S135" s="3"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
+      <c r="O136" s="3"/>
+      <c r="Q136" s="3"/>
+      <c r="R136" s="3"/>
+      <c r="S136" s="3"/>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3"/>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+      <c r="O137" s="3"/>
+      <c r="Q137" s="3"/>
+      <c r="R137" s="3"/>
+      <c r="S137" s="3"/>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3"/>
+      <c r="O138" s="3"/>
+      <c r="Q138" s="3"/>
+      <c r="R138" s="3"/>
+      <c r="S138" s="3"/>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+      <c r="Q139" s="3"/>
+      <c r="R139" s="3"/>
+      <c r="S139" s="3"/>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="3"/>
+      <c r="Q140" s="3"/>
+      <c r="R140" s="3"/>
+      <c r="S140" s="3"/>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="Q141" s="3"/>
+      <c r="R141" s="3"/>
+      <c r="S141" s="3"/>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+      <c r="Q142" s="3"/>
+      <c r="R142" s="3"/>
+      <c r="S142" s="3"/>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+      <c r="Q143" s="3"/>
+      <c r="R143" s="3"/>
+      <c r="S143" s="3"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+      <c r="Q144" s="3"/>
+      <c r="R144" s="3"/>
+      <c r="S144" s="3"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3"/>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3"/>
+      <c r="O145" s="3"/>
+      <c r="Q145" s="3"/>
+      <c r="R145" s="3"/>
+      <c r="S145" s="3"/>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3"/>
+      <c r="O146" s="3"/>
+      <c r="Q146" s="3"/>
+      <c r="R146" s="3"/>
+      <c r="S146" s="3"/>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
+      <c r="Q147" s="3"/>
+      <c r="R147" s="3"/>
+      <c r="S147" s="3"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="3"/>
+      <c r="K148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
+      <c r="O148" s="3"/>
+      <c r="Q148" s="3"/>
+      <c r="R148" s="3"/>
+      <c r="S148" s="3"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3"/>
+      <c r="K149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
+      <c r="Q149" s="3"/>
+      <c r="R149" s="3"/>
+      <c r="S149" s="3"/>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+      <c r="O150" s="3"/>
+      <c r="Q150" s="3"/>
+      <c r="R150" s="3"/>
+      <c r="S150" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{64206B27-AE32-4F62-8478-9641B311CD8A}">
+          <x14:formula1>
+            <xm:f>dropdown!$A$2:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>B7 F7 J7 N7 R7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FD645081-0A03-469E-AFF4-5BBEEF3456EB}">
+          <x14:formula1>
+            <xm:f>dropdown!$C$2:$C$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3 R3 N3 F3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B15852B-C00D-4EB5-A4EB-5D18F2ED4CAE}">
+          <x14:formula1>
+            <xm:f>dropdown!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4 F4 J4 N4 R4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F0CBEA-0A96-42E6-983D-36A2EB3C1E69}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1830F4-F583-4463-B288-16299F799B5E}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="8.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1830F4-F583-4463-B288-16299F799B5E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/core/ecos/dev-template.xlsx
+++ b/core/ecos/dev-template.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\anaconda3\Lib\sprnldata\core\ecos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{881B894D-1018-4A79-93C7-7BAB6FC2177F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0EA5404-030E-4137-847C-0E2509FC8B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28910" yWindow="10" windowWidth="29020" windowHeight="15820" xr2:uid="{36412438-C21D-4853-9A0B-9D97E570583D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="14020" xr2:uid="{36412438-C21D-4853-9A0B-9D97E570583D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
-    <sheet name="dropdown" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="dropdown" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>database</t>
   </si>
@@ -117,23 +118,74 @@
     <t>Q</t>
   </si>
   <si>
-    <t>NGDP</t>
-  </si>
-  <si>
-    <t>BCA_BP6_USD</t>
+    <t>NGDP_RPCH</t>
+  </si>
+  <si>
+    <t>PCPI_PCH</t>
+  </si>
+  <si>
+    <t>BFD_GDP</t>
+  </si>
+  <si>
+    <t>GGXOFB_GDP</t>
+  </si>
+  <si>
+    <t>GGXWDG_GDP</t>
+  </si>
+  <si>
+    <t>BCA_GDP</t>
+  </si>
+  <si>
+    <t>BCA_GDP_BP6</t>
+  </si>
+  <si>
+    <t>BFD_GDP_BP6</t>
+  </si>
+  <si>
+    <t>BMGS_BP6</t>
+  </si>
+  <si>
+    <t>IAR_BP6</t>
+  </si>
+  <si>
+    <t>GGR_GDP</t>
+  </si>
+  <si>
+    <t>GGEI_GDP</t>
+  </si>
+  <si>
+    <t>GGX_GDP</t>
+  </si>
+  <si>
+    <t>GGXCNL_GDP</t>
+  </si>
+  <si>
+    <t>GGXONLB_GDP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -145,6 +197,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,20 +253,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{75F9AED8-5DA5-4B7E-A557-08C6B97F24B9}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{B7E7FFF6-CA34-4617-9FFA-61EB74EB885B}"/>
+    <cellStyle name="Normal 2 2 2" xfId="4" xr:uid="{A2DA767C-635B-41B3-940A-24ED9BD0E64C}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="5" xr:uid="{95212FE2-3CC9-48CE-B5BE-9F7AB5237E5E}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{727B6B13-B9A1-4ECC-9356-68F280613F49}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -583,15 +652,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="1" t="s">
         <v>3</v>
@@ -614,15 +681,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="I4" s="1" t="s">
         <v>4</v>
@@ -645,15 +710,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="C5" s="3"/>
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3">
-        <v>2000</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="1" t="s">
         <v>5</v>
@@ -675,16 +738,12 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
-        <v>2000</v>
-      </c>
+      <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="3">
-        <v>2020</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="I6" s="1" t="s">
         <v>6</v>
@@ -707,15 +766,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3"/>
       <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="1" t="s">
         <v>7</v>
@@ -798,20 +855,14 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>111</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3">
-        <v>111</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -825,7 +876,9 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -842,7 +895,9 @@
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -859,7 +914,9 @@
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -876,7 +933,9 @@
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -893,7 +952,9 @@
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -910,7 +971,9 @@
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -927,7 +990,9 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -944,7 +1009,9 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -961,7 +1028,9 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -978,7 +1047,9 @@
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -995,7 +1066,9 @@
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1012,7 +1085,9 @@
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1029,7 +1104,9 @@
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1046,7 +1123,9 @@
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -3199,6 +3278,9 @@
       <c r="S150" s="3"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:C24">
+    <sortCondition ref="C11:C24"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -3228,6 +3310,81 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5DC8DB-2ED5-4420-8DBD-2419C740FC20}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1830F4-F583-4463-B288-16299F799B5E}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/core/ecos/dev-template.xlsx
+++ b/core/ecos/dev-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\anaconda3\Lib\sprnldata\core\ecos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6CAA57C-E8E6-4141-A1A0-AA4BB9AB8350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB0E791-069F-4AF4-9ABE-D41A0B26900B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="14020" xr2:uid="{36412438-C21D-4853-9A0B-9D97E570583D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>database</t>
   </si>
@@ -115,54 +115,6 @@
   </si>
   <si>
     <t>Q</t>
-  </si>
-  <si>
-    <t>NGDP_RPCH</t>
-  </si>
-  <si>
-    <t>PCPI_PCH</t>
-  </si>
-  <si>
-    <t>BFD_GDP</t>
-  </si>
-  <si>
-    <t>GGXOFB_GDP</t>
-  </si>
-  <si>
-    <t>GGXWDG_GDP</t>
-  </si>
-  <si>
-    <t>BCA_GDP</t>
-  </si>
-  <si>
-    <t>BCA_GDP_BP6</t>
-  </si>
-  <si>
-    <t>BFD_GDP_BP6</t>
-  </si>
-  <si>
-    <t>BMGS_BP6</t>
-  </si>
-  <si>
-    <t>IAR_BP6</t>
-  </si>
-  <si>
-    <t>GGR_GDP</t>
-  </si>
-  <si>
-    <t>GGEI_GDP</t>
-  </si>
-  <si>
-    <t>GGX_GDP</t>
-  </si>
-  <si>
-    <t>GGXCNL_GDP</t>
-  </si>
-  <si>
-    <t>GGXONLB_GDP</t>
-  </si>
-  <si>
-    <t>NGDP_R</t>
   </si>
 </sst>
 </file>
@@ -636,9 +588,7 @@
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="E3" s="4" t="s">
         <v>3</v>
@@ -665,9 +615,7 @@
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
@@ -694,9 +642,7 @@
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2">
-        <v>2000</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="E5" s="4" t="s">
         <v>5</v>
@@ -750,9 +696,7 @@
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="E7" s="4" t="s">
         <v>7</v>
@@ -842,9 +786,7 @@
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -861,9 +803,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -880,9 +820,7 @@
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -899,9 +837,7 @@
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -918,9 +854,7 @@
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -937,9 +871,7 @@
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -956,9 +888,7 @@
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -975,9 +905,7 @@
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -994,9 +922,7 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="C18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1013,9 +939,7 @@
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="C19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1032,9 +956,7 @@
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1051,9 +973,7 @@
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="C21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1070,9 +990,7 @@
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="C22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1089,9 +1007,7 @@
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="C23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1108,9 +1024,7 @@
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="C24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1127,9 +1041,7 @@
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="C25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
